--- a/app/data/input/entregas_exemplo.xlsx
+++ b/app/data/input/entregas_exemplo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janai\OneDrive\Documentos\ProjetoRPA\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janai\OneDrive\Documentos\ProjetoRPA\app\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380CEDAF-9982-43C8-919E-C8F2E63E574E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A44205B-A0CF-4C7C-BF13-19C4D528A157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,7 +440,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>5592993146553</v>
+        <v>5592999833499</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
